--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104639_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104639_W21.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.683</v>
+        <v>4.5262</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2165</v>
+        <v>3.3103</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4666</v>
+        <v>1.2159</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2928</v>
+        <v>1.2986</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7112</v>
+        <v>1.7172</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4185</v>
+        <v>-0.4186</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8363</v>
+        <v>0.8216</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1775</v>
+        <v>1.1721</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4565</v>
+        <v>0.477</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5337</v>
+        <v>0.5451</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5905</v>
+        <v>0.4356</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7561</v>
+        <v>-0.1165</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8344</v>
+        <v>0.5521</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W2" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3735</v>
+        <v>3.3225</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8947000000000001</v>
+        <v>1.0634</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4787</v>
+        <v>2.2591</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2536</v>
+        <v>1.2622</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8525</v>
+        <v>1.8515</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6202</v>
+        <v>1.6051</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1002</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7139</v>
+        <v>1.7052</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3666</v>
+        <v>-0.3428</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5359</v>
+        <v>-0.6015</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8861</v>
+        <v>-0.6995</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3502</v>
+        <v>0.098</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0665</v>
+        <v>2.2513</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8208</v>
+        <v>0.8098</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2457</v>
+        <v>1.4415</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8536</v>
+        <v>1.8494</v>
       </c>
       <c r="H4" t="n">
-        <v>0.974</v>
+        <v>0.9737</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8796</v>
+        <v>0.8757</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2563</v>
+        <v>1.2465</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2407</v>
+        <v>-0.0534</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0321</v>
+        <v>0.1557</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. BROOKS</t>
+          <t>A. REYES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.887</v>
+        <v>2.1983</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4926</v>
+        <v>2.7897</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3943</v>
+        <v>-0.5914</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7007</v>
+        <v>1.8186</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0432</v>
+        <v>-0.8278</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6575</v>
+        <v>2.6464</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1451</v>
+        <v>3.1511</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3117</v>
+        <v>0.1207</v>
       </c>
       <c r="L5" t="n">
-        <v>2.8334</v>
+        <v>3.0304</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4444</v>
+        <v>-1.3325</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2685</v>
+        <v>-0.9485</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1759</v>
+        <v>-0.384</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>2.9592</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7891</v>
+        <v>-0.669</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.747</v>
+        <v>-0.6298</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0421</v>
+        <v>-0.0392</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7712</v>
+        <v>1.6342</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. REYES</t>
+          <t>E. BROOKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6942</v>
+        <v>2.1661</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6345</v>
+        <v>0.7789</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9403</v>
+        <v>1.3872</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8201</v>
+        <v>2.7041</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.84</v>
+        <v>0.0513</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6601</v>
+        <v>2.6528</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1731</v>
+        <v>3.1326</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1212</v>
+        <v>0.3103</v>
       </c>
       <c r="L6" t="n">
-        <v>3.0519</v>
+        <v>2.8223</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.353</v>
+        <v>-0.4285</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.259</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3918</v>
+        <v>-0.1695</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9488</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1674</v>
+        <v>-0.5168</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8166</v>
+        <v>-0.4416</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3508</v>
+        <v>-0.0752</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5463</v>
+        <v>-0.9317</v>
       </c>
       <c r="W6" t="n">
-        <v>1.639</v>
+        <v>-0.7739</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1853</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5765</v>
+        <v>1.286</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4264</v>
+        <v>0.3023</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1501</v>
+        <v>0.9837</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5515</v>
+        <v>-0.5425</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2052</v>
+        <v>-0.1978</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2661</v>
+        <v>0.2584</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8176</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6763</v>
+        <v>0.3717</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3871</v>
+        <v>0.2715</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2891</v>
+        <v>0.1002</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2951</v>
+        <v>0.7176</v>
       </c>
       <c r="E8" t="n">
-        <v>0.631</v>
+        <v>0.9706</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3358</v>
+        <v>-0.253</v>
       </c>
       <c r="G8" t="n">
-        <v>1.386</v>
+        <v>1.3945</v>
       </c>
       <c r="H8" t="n">
-        <v>1.466</v>
+        <v>1.4703</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0799</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4573</v>
+        <v>1.4507</v>
       </c>
       <c r="K8" t="n">
-        <v>1.42</v>
+        <v>1.4134</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0712</v>
+        <v>-0.0562</v>
       </c>
       <c r="N8" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.796</v>
+        <v>-0.3809</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3992</v>
+        <v>-0.0444</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3968</v>
+        <v>-0.3366</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5525</v>
+        <v>-0.4044</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7866</v>
+        <v>-1.8919</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2341</v>
+        <v>1.4875</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3901</v>
+        <v>-0.4129</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.7225</v>
+        <v>-2.7472</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3324</v>
+        <v>2.3343</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5815</v>
+        <v>0.5312</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.7295</v>
+        <v>-1.7699</v>
       </c>
       <c r="L9" t="n">
-        <v>2.3109</v>
+        <v>2.301</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9716</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.48</v>
+        <v>-0.3101</v>
       </c>
       <c r="T9" t="n">
-        <v>0.127</v>
+        <v>0.0809</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.607</v>
+        <v>-0.391</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0956</v>
+        <v>-1.0296</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.274</v>
+        <v>-0.2023</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8216</v>
+        <v>-0.8273</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5248</v>
+        <v>0.5135</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7994</v>
+        <v>0.7985</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2746</v>
+        <v>-0.285</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4996</v>
+        <v>1.4724</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9107</v>
+        <v>0.8996</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5889</v>
+        <v>0.5728</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9749</v>
+        <v>-0.9588</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.284</v>
+        <v>-0.1985</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5565</v>
+        <v>-0.4392</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2725</v>
+        <v>0.2407</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8197</v>
+        <v>-2.1983</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6136</v>
+        <v>0.3619</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4333</v>
+        <v>-2.5602</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3712</v>
+        <v>-0.3618</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.091</v>
+        <v>-1.0859</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7197</v>
+        <v>0.7241</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2695</v>
+        <v>1.2589</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3739</v>
+        <v>0.3652</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8956</v>
+        <v>0.8937</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6407</v>
+        <v>-1.6207</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1225</v>
+        <v>-0.2706</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3176</v>
+        <v>0.0834</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1951</v>
+        <v>-0.354</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8831</v>
+        <v>-5.2579</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.936</v>
+        <v>-3.4958</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.947</v>
+        <v>-1.7621</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0801</v>
+        <v>-2.0825</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0721</v>
+        <v>-2.0736</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.008</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7452</v>
+        <v>-1.7686</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.4413</v>
+        <v>-1.4554</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3348</v>
+        <v>-0.3139</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.803</v>
+        <v>-0.1754</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4688</v>
+        <v>0.0044</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3342</v>
+        <v>-0.1797</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.224900000000001</v>
+        <v>7.577800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>4.733500000000001</v>
+        <v>4.796899999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4915</v>
+        <v>2.7809</v>
       </c>
       <c r="G13" t="n">
-        <v>7.438700000000001</v>
+        <v>7.4412</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.6771</v>
+        <v>-2.6575</v>
       </c>
       <c r="I13" t="n">
-        <v>10.1156</v>
+        <v>10.0986</v>
       </c>
       <c r="J13" t="n">
-        <v>13.3598</v>
+        <v>13.1599</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9785</v>
+        <v>1.8726</v>
       </c>
       <c r="L13" t="n">
-        <v>11.3811</v>
+        <v>11.287</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.920999999999999</v>
+        <v>-5.7186</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.6555</v>
+        <v>-4.5304</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2656</v>
+        <v>-1.1882</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2684</v>
+        <v>2.276299999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7442</v>
+        <v>-14.7961</v>
       </c>
       <c r="R13" t="n">
-        <v>17.0125</v>
+        <v>17.0724</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.7068</v>
+        <v>-2.3689</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.4951</v>
+        <v>-2.1399</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2119</v>
+        <v>-0.2289999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2248999999999997</v>
+        <v>0.2291999999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>8.613000000000001</v>
+        <v>8.572900000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.388</v>
+        <v>-8.3436</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7458</v>
+        <v>4.999</v>
       </c>
       <c r="E14" t="n">
-        <v>7.802</v>
+        <v>6.9286</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0561</v>
+        <v>-1.9296</v>
       </c>
       <c r="G14" t="n">
-        <v>0.632</v>
+        <v>0.6287</v>
       </c>
       <c r="H14" t="n">
-        <v>1.397</v>
+        <v>1.385</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2777</v>
+        <v>3.2506</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5314</v>
+        <v>2.5059</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.6457</v>
+        <v>-2.6219</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6751</v>
+        <v>-0.0558</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8075</v>
+        <v>-0.0166</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1325</v>
+        <v>-0.0392</v>
       </c>
       <c r="V14" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="W14" t="n">
-        <v>5.0777</v>
+        <v>5.0604</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8535</v>
+        <v>2.0997</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8952</v>
+        <v>0.9794</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9583</v>
+        <v>1.1203</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7696</v>
+        <v>1.7729</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1427</v>
+        <v>2.1453</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6984</v>
+        <v>3.6749</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2858</v>
+        <v>2.2753</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4126</v>
+        <v>1.3997</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9289</v>
+        <v>-1.902</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.7858</v>
+        <v>-1.772</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2129</v>
+        <v>0.0324</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6049</v>
+        <v>-0.486</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3919</v>
+        <v>0.5184</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3606</v>
+        <v>0.8696</v>
       </c>
       <c r="E16" t="n">
-        <v>0.484</v>
+        <v>0.8235</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1234</v>
+        <v>0.046</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7548</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3407</v>
+        <v>-0.3336</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0955</v>
+        <v>1.0902</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5965</v>
+        <v>1.588</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5273</v>
+        <v>1.519</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8417</v>
+        <v>-0.8314</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1921</v>
+        <v>0.3194</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1391</v>
+        <v>0.2159</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0529</v>
+        <v>0.1035</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. GUERRA</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2602</v>
+        <v>-0.2259</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6044</v>
+        <v>1.3552</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8646</v>
+        <v>-1.581</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0973</v>
+        <v>-1.7541</v>
       </c>
       <c r="H17" t="n">
-        <v>0.593</v>
+        <v>1.3724</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6903</v>
+        <v>-3.1266</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.1404</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1456</v>
+        <v>0.9997</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0746</v>
+        <v>-1.1401</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0263</v>
+        <v>-1.6138</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7387</v>
+        <v>0.3727</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7649</v>
+        <v>-1.9865</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>-0.4553</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>2.5039</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4897</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>1.733</v>
+        <v>-0.2281</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7567</v>
+        <v>0.7972</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7712</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.7712</v>
+        <v>2.1789</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>F. GUERRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3607</v>
+        <v>-0.8173</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1427</v>
+        <v>-2.7982</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5034</v>
+        <v>1.9809</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7644</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3649</v>
+        <v>0.5944</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.1293</v>
+        <v>-0.6819</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1232</v>
+        <v>-0.0774</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0044</v>
+        <v>-0.1519</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1276</v>
+        <v>0.0745</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6411</v>
+        <v>-0.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3605</v>
+        <v>0.7463</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.0017</v>
+        <v>-0.7563</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0415</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.4537</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4952</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4549</v>
+        <v>1.4099</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4657</v>
+        <v>0.5571</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9206</v>
+        <v>0.8528</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>-0.7739</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1853</v>
+        <v>-0.7739</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>B. FITIPALDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1243</v>
+        <v>-1.5141</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2371</v>
+        <v>0.2377</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8872</v>
+        <v>-1.7517</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5951</v>
+        <v>-0.4688</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5707</v>
+        <v>-0.9709</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9755</v>
+        <v>0.502</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8763</v>
+        <v>0.4307</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0283</v>
+        <v>-1.2001</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.152</v>
+        <v>1.6308</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2812</v>
+        <v>-0.8995</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4576</v>
+        <v>0.2292</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8236</v>
+        <v>-1.1287</v>
       </c>
       <c r="P19" t="n">
-        <v>-4.083</v>
+        <v>1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.8976</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8172</v>
+        <v>-0.0743</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5989</v>
+        <v>0.0346</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2184</v>
+        <v>-0.1089</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5463</v>
+        <v>-2.3367</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.639</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.438</v>
+        <v>-1.52</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.2088</v>
+        <v>-3.7639</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7708</v>
+        <v>2.2439</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2231</v>
+        <v>-3.223</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4661</v>
+        <v>-2.4616</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.757</v>
+        <v>-0.7614</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.1869</v>
+        <v>-3.2105</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.134</v>
+        <v>-2.1448</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.053</v>
+        <v>-1.0656</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0362</v>
+        <v>-0.0125</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2129</v>
+        <v>0.7014</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0484</v>
+        <v>0.427</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1645</v>
+        <v>0.2744</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. FITIPALDO</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4975</v>
+        <v>-2.0847</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3358</v>
+        <v>-1.7959</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1617</v>
+        <v>-0.2888</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4715</v>
+        <v>0.5552</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9726</v>
+        <v>1.5247</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5011</v>
+        <v>-0.9695</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4475</v>
+        <v>1.8139</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1917</v>
+        <v>1.9705</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6392</v>
+        <v>-0.1566</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-1.2587</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2192</v>
+        <v>-0.4458</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1381</v>
+        <v>-0.8129</v>
       </c>
       <c r="P21" t="n">
-        <v>1.361</v>
+        <v>-4.0974</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-5.9184</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.041</v>
+        <v>0.9127</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5565</v>
+        <v>0.1297</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4845</v>
+        <v>0.7831</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.3461</v>
+        <v>0.5447</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3461</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7024</v>
+        <v>-2.6131</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8114</v>
+        <v>-0.4607</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8909</v>
+        <v>-2.1524</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9371</v>
+        <v>-1.9278</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6524</v>
+        <v>-0.6438</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2848</v>
+        <v>-1.284</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5332</v>
+        <v>-0.5373</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4039</v>
+        <v>-1.3906</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4201</v>
+        <v>0.4936</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2782</v>
+        <v>0.0765</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6983</v>
+        <v>0.4171</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3221</v>
+        <v>-4.8432</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6178</v>
+        <v>-4.2866</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7043</v>
+        <v>-0.5566</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6968</v>
+        <v>-3.6934</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0403</v>
+        <v>0.0457</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.7371</v>
+        <v>-3.739</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.061</v>
+        <v>-1.0739</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1649</v>
+        <v>-1.1773</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6357</v>
+        <v>-2.6194</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.5721</v>
+        <v>-2.5617</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4912</v>
+        <v>-0.0117</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8347</v>
+        <v>-0.4811</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3436</v>
+        <v>0.4694</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.224900000000002</v>
+        <v>-5.650000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.491400000000001</v>
+        <v>-2.7809</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.7333</v>
+        <v>-2.868999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.438700000000001</v>
+        <v>-7.4411</v>
       </c>
       <c r="H24" t="n">
-        <v>2.6768</v>
+        <v>2.657600000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-10.1155</v>
+        <v>-10.0989</v>
       </c>
       <c r="J24" t="n">
-        <v>5.9211</v>
+        <v>5.718599999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>4.655700000000001</v>
+        <v>4.5303</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2654</v>
+        <v>1.188399999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-13.3596</v>
+        <v>-13.1598</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.9786</v>
+        <v>-1.8728</v>
       </c>
       <c r="O24" t="n">
-        <v>-11.3811</v>
+        <v>-11.2871</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.2684</v>
+        <v>-2.276400000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-17.0125</v>
+        <v>-17.0724</v>
       </c>
       <c r="R24" t="n">
-        <v>14.7443</v>
+        <v>14.7961</v>
       </c>
       <c r="S24" t="n">
-        <v>2.706900000000001</v>
+        <v>4.2967</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2119</v>
+        <v>0.2290000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>2.4951</v>
+        <v>4.0678</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2248999999999997</v>
+        <v>-0.2293000000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>8.388</v>
+        <v>8.343699999999998</v>
       </c>
       <c r="X24" t="n">
-        <v>-8.613099999999999</v>
+        <v>-8.572900000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104639_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104639_W21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.3436</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104639_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-8.572900000000001</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
